--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57428</v>
+        <v>57431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57431</v>
+        <v>57437</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57441</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57667</v>
+        <v>57693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57693</v>
+        <v>57695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57695</v>
+        <v>57703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57703</v>
+        <v>57704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57704</v>
+        <v>57705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12887-2024 artfynd.xlsx
+++ b/artfynd/A 12887-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>123305962</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
